--- a/projetos/excel/dashboard-vendas-game-pass/dashboard-vendas-game-pass.xlsx
+++ b/projetos/excel/dashboard-vendas-game-pass/dashboard-vendas-game-pass.xlsx
@@ -281,6 +281,7 @@
           </a:p>
         </rich>
       </tx>
+      <overlay val="0"/>
     </title>
     <plotArea>
       <barChart>
@@ -306,9 +307,9 @@
             </a:ln>
           </spPr>
           <cat>
-            <numRef>
+            <strRef>
               <f>'Cálculos'!$A$13:$A$15</f>
-            </numRef>
+            </strRef>
           </cat>
           <val>
             <numRef>
@@ -347,7 +348,16 @@
         </scaling>
         <delete val="0"/>
         <axPos val="l"/>
-        <majorGridlines/>
+        <majorGridlines>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="6350">
+              <a:solidFill>
+                <a:srgbClr val="D9D9D9"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+        </majorGridlines>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <crossAx val="10"/>
@@ -376,6 +386,7 @@
           </a:p>
         </rich>
       </tx>
+      <overlay val="0"/>
     </title>
     <plotArea>
       <barChart>
@@ -401,9 +412,9 @@
             </a:ln>
           </spPr>
           <cat>
-            <numRef>
+            <strRef>
               <f>'Cálculos'!$A$18:$A$20</f>
-            </numRef>
+            </strRef>
           </cat>
           <val>
             <numRef>
@@ -442,7 +453,16 @@
         </scaling>
         <delete val="0"/>
         <axPos val="l"/>
-        <majorGridlines/>
+        <majorGridlines>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="6350">
+              <a:solidFill>
+                <a:srgbClr val="D9D9D9"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+        </majorGridlines>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <crossAx val="10"/>
@@ -471,6 +491,7 @@
           </a:p>
         </rich>
       </tx>
+      <overlay val="0"/>
     </title>
     <plotArea>
       <pieChart>
@@ -511,9 +532,9 @@
             </spPr>
           </dPt>
           <cat>
-            <numRef>
+            <strRef>
               <f>'Cálculos'!$A$23:$A$24</f>
-            </numRef>
+            </strRef>
           </cat>
           <val>
             <numRef>
@@ -557,6 +578,7 @@
           </a:p>
         </rich>
       </tx>
+      <overlay val="0"/>
     </title>
     <plotArea>
       <lineChart>
@@ -589,9 +611,9 @@
             </spPr>
           </marker>
           <cat>
-            <numRef>
+            <strRef>
               <f>'Cálculos'!$A$27:$A$38</f>
-            </numRef>
+            </strRef>
           </cat>
           <val>
             <numRef>
@@ -623,7 +645,16 @@
         </scaling>
         <delete val="0"/>
         <axPos val="l"/>
-        <majorGridlines/>
+        <majorGridlines>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="6350">
+              <a:solidFill>
+                <a:srgbClr val="D9D9D9"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+        </majorGridlines>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <crossAx val="10"/>
@@ -652,6 +683,7 @@
           </a:p>
         </rich>
       </tx>
+      <overlay val="0"/>
     </title>
     <plotArea>
       <barChart>
@@ -677,9 +709,9 @@
             </a:ln>
           </spPr>
           <cat>
-            <numRef>
+            <strRef>
               <f>'Cálculos'!$A$42:$A$43</f>
-            </numRef>
+            </strRef>
           </cat>
           <val>
             <numRef>
@@ -718,7 +750,16 @@
         </scaling>
         <delete val="0"/>
         <axPos val="l"/>
-        <majorGridlines/>
+        <majorGridlines>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="6350">
+              <a:solidFill>
+                <a:srgbClr val="D9D9D9"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+        </majorGridlines>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <crossAx val="10"/>
@@ -747,6 +788,7 @@
           </a:p>
         </rich>
       </tx>
+      <overlay val="0"/>
     </title>
     <plotArea>
       <barChart>
@@ -772,9 +814,9 @@
             </a:ln>
           </spPr>
           <cat>
-            <numRef>
+            <strRef>
               <f>'Cálculos'!$A$13:$A$15</f>
-            </numRef>
+            </strRef>
           </cat>
           <val>
             <numRef>
@@ -813,7 +855,16 @@
         </scaling>
         <delete val="0"/>
         <axPos val="l"/>
-        <majorGridlines/>
+        <majorGridlines>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="6350">
+              <a:solidFill>
+                <a:srgbClr val="D9D9D9"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+        </majorGridlines>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <crossAx val="10"/>
